--- a/diseases/d113/2005-2009.xlsx
+++ b/diseases/d113/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -4861,9 +4858,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -5257,9 +5251,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5701,9 +5692,6 @@
       <c r="O34" t="n">
         <v>1</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -6145,9 +6133,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6589,9 +6574,6 @@
       <c r="O40" t="n">
         <v>1</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -7033,9 +7015,6 @@
       <c r="O43" t="n">
         <v>1</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -7477,9 +7456,6 @@
       <c r="O46" t="n">
         <v>0</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0</v>
       </c>
@@ -7921,9 +7897,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -8365,9 +8338,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.002083050494133427</v>
       </c>
@@ -8809,9 +8779,6 @@
       <c r="O55" t="n">
         <v>2</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.004166100988266854</v>
       </c>
@@ -9253,9 +9220,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9697,9 +9661,6 @@
       <c r="O61" t="n">
         <v>0</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
@@ -10141,9 +10102,6 @@
       <c r="O64" t="n">
         <v>0</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
@@ -10585,9 +10543,6 @@
       <c r="O67" t="n">
         <v>1</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.3208722591492714</v>
       </c>
@@ -10981,9 +10936,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11425,9 +11377,6 @@
       <c r="O72" t="n">
         <v>0</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0</v>
       </c>
@@ -11869,9 +11818,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -12313,9 +12259,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -12757,9 +12700,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -13201,9 +13141,6 @@
       <c r="O84" t="n">
         <v>5</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.010378155386039</v>
       </c>
@@ -13645,9 +13582,6 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -14089,9 +14023,6 @@
       <c r="O90" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.004151262154415599</v>
       </c>
@@ -14533,9 +14464,6 @@
       <c r="O93" t="n">
         <v>1</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -14977,9 +14905,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15421,9 +15346,6 @@
       <c r="O99" t="n">
         <v>1</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -15865,9 +15787,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.002075631077207799</v>
       </c>
@@ -16309,9 +16228,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -16705,9 +16621,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -17149,9 +17062,6 @@
       <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -17593,9 +17503,6 @@
       <c r="O113" t="n">
         <v>4</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -18037,9 +17944,6 @@
       <c r="O116" t="n">
         <v>5</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01033987307557643</v>
       </c>
@@ -18481,9 +18385,6 @@
       <c r="O119" t="n">
         <v>4</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.008271898460461143</v>
       </c>
@@ -18925,9 +18826,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19517,9 +19415,6 @@
       <c r="O126" t="n">
         <v>1</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -20109,9 +20004,6 @@
       <c r="O130" t="n">
         <v>0</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0</v>
       </c>
@@ -20701,9 +20593,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.004135949230230571</v>
       </c>
@@ -21293,9 +21182,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -21885,9 +21771,6 @@
       <c r="O142" t="n">
         <v>1</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.002067974615115286</v>
       </c>
@@ -22477,9 +22360,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -23069,9 +22949,6 @@
       <c r="O150" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0</v>
       </c>
@@ -23465,9 +23342,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -24057,9 +23931,6 @@
       <c r="O156" t="n">
         <v>3</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -24649,9 +24520,6 @@
       <c r="O160" t="n">
         <v>2</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -25241,9 +25109,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -25833,9 +25698,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -26425,9 +26287,6 @@
       <c r="O172" t="n">
         <v>3</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.00617961845861509</v>
       </c>
@@ -27017,9 +26876,6 @@
       <c r="O176" t="n">
         <v>1</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.002059872819538363</v>
       </c>
@@ -27609,9 +27465,6 @@
       <c r="O180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -28201,9 +28054,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -28793,9 +28643,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -29385,9 +29232,6 @@
       <c r="O192" t="n">
         <v>2</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.004119745639076727</v>
       </c>
@@ -29975,9 +29819,6 @@
         <v>0</v>
       </c>
       <c r="O196" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q196" t="n">
         <v>0</v>
       </c>
       <c r="R196" t="n">
